--- a/plantillas/FORMATO DE ENTREGA LOCAL limpia.xlsx
+++ b/plantillas/FORMATO DE ENTREGA LOCAL limpia.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ventas8td\Desktop\HOJAS DE RUTA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salva\OneDrive\Documentos\TD_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC54A2F-B4A5-423A-BE17-B7FA8271D1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17970" windowHeight="6030"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,12 +29,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>T&amp;D</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -58,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="0" shapeId="0">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>VENDEDOR:</t>
   </si>
@@ -200,23 +201,17 @@
     <t>NO APLICA</t>
   </si>
   <si>
-    <t>ALEX</t>
-  </si>
-  <si>
     <t>MONTERREY</t>
-  </si>
-  <si>
-    <t>8112450400</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -461,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -485,12 +480,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -512,8 +501,44 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -521,42 +546,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -578,29 +570,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,255 +875,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="23" style="1" customWidth="1"/>
     <col min="6" max="6" width="24" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="30.5546875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.5" customHeight="1"/>
-    <row r="2" spans="1:12" ht="33" customHeight="1">
+    <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:12" ht="25.5" customHeight="1">
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+    </row>
+    <row r="3" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-    </row>
-    <row r="4" spans="1:12" ht="25.5" customHeight="1">
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+    </row>
+    <row r="4" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="47" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="49"/>
-    </row>
-    <row r="5" spans="1:12" ht="25.5" customHeight="1">
+      <c r="F4" s="27"/>
+      <c r="G4" s="28"/>
+    </row>
+    <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27"/>
-    </row>
-    <row r="6" spans="1:12" ht="25.5" customHeight="1">
+      <c r="B5" s="32"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="43"/>
+    </row>
+    <row r="6" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="15"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27"/>
-    </row>
-    <row r="8" spans="1:12" ht="25.5" customHeight="1">
+      <c r="D7" s="16"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
+    </row>
+    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>38</v>
-      </c>
+      <c r="B8" s="17"/>
       <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="27"/>
-    </row>
-    <row r="9" spans="1:12" ht="25.5" customHeight="1">
+      <c r="D8" s="14"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+    </row>
+    <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="30"/>
-    </row>
-    <row r="10" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A10" s="23" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="46"/>
+    </row>
+    <row r="10" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="10" t="s">
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="20"/>
-    </row>
-    <row r="11" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A11" s="23" t="s">
+      <c r="G10" s="47"/>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="13" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:12" ht="25.5" customHeight="1">
-      <c r="A12" s="44" t="s">
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="13" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:12" ht="25.5" customHeight="1"/>
-    <row r="14" spans="1:12" ht="30" customHeight="1"/>
-    <row r="15" spans="1:12" ht="25.5" customHeight="1"/>
-    <row r="16" spans="1:12" ht="25.5" customHeight="1">
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17" ht="25.5" customHeight="1"/>
-    <row r="18" ht="25.5" customHeight="1"/>
-    <row r="19" ht="25.5" customHeight="1"/>
-    <row r="20" ht="25.5" customHeight="1"/>
-    <row r="21" ht="25.5" customHeight="1"/>
-    <row r="22" ht="25.5" customHeight="1"/>
-    <row r="23" ht="25.5" customHeight="1"/>
-    <row r="24" ht="30.75" customHeight="1"/>
-    <row r="25" ht="25.5" customHeight="1"/>
-    <row r="26" ht="25.5" customHeight="1"/>
-    <row r="27" ht="25.5" customHeight="1"/>
-    <row r="28" ht="25.5" customHeight="1"/>
-    <row r="29" ht="25.5" customHeight="1"/>
-    <row r="30" ht="25.5" customHeight="1"/>
-    <row r="31" ht="25.5" customHeight="1"/>
-    <row r="32" ht="25.5" customHeight="1"/>
-    <row r="33" ht="25.5" customHeight="1"/>
-    <row r="34" ht="25.5" customHeight="1"/>
-    <row r="35" ht="25.5" customHeight="1"/>
-    <row r="36" ht="25.5" customHeight="1"/>
-    <row r="37" ht="25.5" customHeight="1"/>
-    <row r="38" ht="25.5" customHeight="1"/>
-    <row r="39" ht="25.5" customHeight="1"/>
-    <row r="40" ht="25.5" customHeight="1"/>
-    <row r="41" ht="25.5" customHeight="1"/>
-    <row r="42" ht="25.5" customHeight="1"/>
-    <row r="43" ht="25.5" customHeight="1"/>
-    <row r="44" ht="25.5" customHeight="1"/>
-    <row r="45" ht="25.5" customHeight="1"/>
-    <row r="46" ht="25.5" customHeight="1"/>
-    <row r="47" ht="25.5" customHeight="1"/>
-    <row r="48" ht="25.5" customHeight="1"/>
-    <row r="49" ht="25.5" customHeight="1"/>
-    <row r="50" ht="25.5" customHeight="1"/>
-    <row r="51" ht="25.5" customHeight="1"/>
-    <row r="52" ht="25.5" customHeight="1"/>
-    <row r="53" ht="25.5" customHeight="1"/>
-    <row r="54" ht="25.5" customHeight="1"/>
-    <row r="55" ht="25.5" customHeight="1"/>
-    <row r="56" ht="25.5" customHeight="1"/>
-    <row r="57" ht="25.5" customHeight="1"/>
-    <row r="58" ht="25.5" customHeight="1"/>
-    <row r="59" ht="25.5" customHeight="1"/>
-    <row r="60" ht="25.5" customHeight="1"/>
-    <row r="61" ht="25.5" customHeight="1"/>
-    <row r="62" ht="25.5" customHeight="1"/>
-    <row r="63" ht="25.5" customHeight="1"/>
-    <row r="64" ht="25.5" customHeight="1"/>
-    <row r="65" ht="25.5" customHeight="1"/>
-    <row r="66" ht="25.5" customHeight="1"/>
-    <row r="67" ht="25.5" customHeight="1"/>
-    <row r="68" ht="25.5" customHeight="1"/>
-    <row r="69" ht="25.5" customHeight="1"/>
-    <row r="70" ht="25.5" customHeight="1"/>
-    <row r="71" ht="25.5" customHeight="1"/>
-    <row r="72" ht="25.5" customHeight="1"/>
-    <row r="73" ht="25.5" customHeight="1"/>
-    <row r="74" ht="25.5" customHeight="1"/>
-    <row r="75" ht="25.5" customHeight="1"/>
-    <row r="76" ht="25.5" customHeight="1"/>
-    <row r="77" ht="25.5" customHeight="1"/>
-    <row r="78" ht="25.5" customHeight="1"/>
-    <row r="79" ht="25.5" customHeight="1"/>
-    <row r="80" ht="25.5" customHeight="1"/>
-    <row r="81" ht="25.5" customHeight="1"/>
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" ht="30.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A10:C10"/>
@@ -1144,6 +1115,12 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="92" fitToHeight="0" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1151,25 +1128,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Hoja2!$C$14:$C$18</xm:f>
           </x14:formula1>
           <xm:sqref>D10:E10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Hoja2!$C$21:$C$26</xm:f>
           </x14:formula1>
           <xm:sqref>D11:E11</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Hoja2!$C$30:$C$33</xm:f>
           </x14:formula1>
           <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>Hoja2!$C$36:$C$38</xm:f>
           </x14:formula1>
@@ -1182,99 +1159,99 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C14:C38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="14" spans="3:3">
+    <row r="14" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="3:3">
+    <row r="15" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="3:3">
+    <row r="16" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="3:3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="3:3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="3:3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="3:3">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="3:3">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="3:3">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="3:3">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="3:3">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:3">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="3:3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="3:3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="3:3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="3:3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>36</v>
       </c>

--- a/plantillas/FORMATO DE ENTREGA LOCAL limpia.xlsx
+++ b/plantillas/FORMATO DE ENTREGA LOCAL limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salva\OneDrive\Documentos\TD_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC54A2F-B4A5-423A-BE17-B7FA8271D1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83E4873-F35F-4A60-91EC-1A6C422B8570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
   <si>
     <t>VENDEDOR:</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>NO APLICA</t>
-  </si>
-  <si>
-    <t>MONTERREY</t>
   </si>
 </sst>
 </file>
@@ -211,7 +208,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,12 +227,6 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Maiandra GD"/>
       <family val="2"/>
     </font>
     <font>
@@ -272,16 +263,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF212529"/>
-      <name val="Arial"/>
+      <name val="Maiandra GD"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -456,16 +440,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -474,17 +458,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -496,43 +477,44 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -540,55 +522,31 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -897,147 +855,147 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="26" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="34"/>
     </row>
     <row r="5" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="8"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="43"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="15" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="21"/>
+      <c r="L6" s="9"/>
+    </row>
+    <row r="7" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="43"/>
-    </row>
-    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D7" s="13"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="21"/>
+    </row>
+    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
     </row>
     <row r="9" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="46"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="47"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="11" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="11" t="s">
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="12"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F16" s="9"/>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1106,6 +1064,12 @@
     <row r="81" ht="25.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="A10:C10"/>
@@ -1115,12 +1079,6 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="92" fitToHeight="0" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1150,7 +1108,7 @@
           <x14:formula1>
             <xm:f>Hoja2!$C$36:$C$38</xm:f>
           </x14:formula1>
-          <xm:sqref>B7</xm:sqref>
+          <xm:sqref>B7:B8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
